--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA/b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA/b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Investigacion.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Firmaron inducción 2026-1</t>
+          <t>Asistieron a la inducción 2026-1</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -684,7 +684,7 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>5</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Inducción 2026-1: 5 estudiantes de Investigación firmaron la planilla (cohorte 2026-1 admitida: 6)</t>
+          <t>Inducción 2026-1: 5 estudiantes de Investigación asistieron (cohorte 2026-1 admitida: 6)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
